--- a/astro-site/public/dl/pack-appcc/15-guia-inspeccion-sanidad.xlsx
+++ b/astro-site/public/dl/pack-appcc/15-guia-inspeccion-sanidad.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="25 Puntos Inspección" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 Puntos Inspección" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'25 Puntos Inspección'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -114,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -136,45 +138,91 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -534,15 +582,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -550,6 +599,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -557,9 +607,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -591,17 +639,23 @@
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>▸ Basada en la experiencia de 15 años de consultoría gastronómica</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+          <t>▸ Basada en la experiencia de John Guerrero: consultor gastronómico desde 2010, en cocina desde los 17 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -609,7 +663,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -618,16 +681,16 @@
   <sheetPr>
     <tabColor rgb="00F44336"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="6"/>
-    <col customWidth="1" max="2" min="2" width="30"/>
-    <col customWidth="1" max="3" min="3" width="50"/>
-    <col customWidth="1" max="4" min="4" width="15"/>
-    <col customWidth="1" max="5" min="5" width="25"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -644,6 +707,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -677,10 +741,10 @@
           <t>DOCUMENTACIÓN</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="20" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -787,16 +851,17 @@
       </c>
       <c r="E10" s="12" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>TEMPERATURAS</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -882,16 +947,17 @@
       </c>
       <c r="E16" s="12" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>HIGIENE Y LIMPIEZA</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="20" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -998,16 +1064,17 @@
       </c>
       <c r="E23" s="12" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>ALMACENAMIENTO</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="20" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -1114,16 +1181,17 @@
       </c>
       <c r="E30" s="12" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>MANIPULACIÓN Y SERVICIO</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="20" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
@@ -1209,6 +1277,7 @@
       </c>
       <c r="E36" s="12" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="B38" s="14" t="inlineStr">
         <is>
@@ -1224,7 +1293,7 @@
       </c>
       <c r="C39" s="14">
         <f>COUNTIF(E5:E37,"✓ Cumple")</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -1235,7 +1304,7 @@
       </c>
       <c r="C40" s="16">
         <f>COUNTIF(E5:E37,"⚠ Mejorar")</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -1246,9 +1315,10 @@
       </c>
       <c r="C41" s="17">
         <f>COUNTIF(E5:E37,"✗ No cumple")</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
@@ -1273,11 +1343,19 @@
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E13 E14 E15 E16 E19 E20 E21 E22 E23 E26 E27 E28 E29 E30 E33 E34 E35 E36" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E13 E14 E15 E16 E19 E20 E21 E22 E23 E26 E27 E28 E29 E30 E33 E34 E35 E36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓ Cumple,⚠ Mejorar,✗ No cumple"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/15-guia-inspeccion-sanidad.xlsx
+++ b/astro-site/public/dl/pack-appcc/15-guia-inspeccion-sanidad.xlsx
@@ -1938,18 +1938,18 @@
     <row r="96"/>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="B70:E70"/>
     <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B70:E70"/>
     <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B47:E47"/>
     <mergeCell ref="A38:D38"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="B56:E56"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B69:E69"/>
     <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B69:E69"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="B74:E74"/>
     <mergeCell ref="A45:E45"/>
@@ -1957,36 +1957,36 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B71:E71"/>
     <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B71:E71"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="B77:E77"/>
     <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B77:E77"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B65:E65"/>
     <mergeCell ref="A29:E29"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B62:E62"/>
     <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B76:E76"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B76:E76"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A80:E80"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B64:E64"/>
     <mergeCell ref="B61:E61"/>
     <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A81:E81"/>
     <mergeCell ref="B53:E53"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:E10">
